--- a/output/pdf_financials_xlsx/MXL.H.xlsx
+++ b/output/pdf_financials_xlsx/MXL.H.xlsx
@@ -4891,13 +4891,13 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>0</v>
+        <v>-0.459987</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0</v>
+        <v>-0.87126</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0.416942</v>
+        <v>-0.12957</v>
       </c>
       <c r="E118" s="3" t="n">
         <v>0</v>
@@ -14602,7 +14602,11 @@
           <t>Exploration and evaluation assets expenditures</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr"/>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E141" t="inlineStr">
         <is>
           <t>-</t>
@@ -15978,7 +15982,11 @@
           <t>Exploration and evaluation assets expenditures (Note 10)</t>
         </is>
       </c>
-      <c r="D162" t="inlineStr"/>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E162" t="inlineStr">
         <is>
           <t>-</t>
@@ -17690,7 +17698,11 @@
           <t>Exploration and evaluation assets expenditures (Note 11)</t>
         </is>
       </c>
-      <c r="D188" t="inlineStr"/>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E188" s="5" t="n">
         <v>-0.459987</v>
       </c>

--- a/output/pdf_financials_xlsx/MXL.H.xlsx
+++ b/output/pdf_financials_xlsx/MXL.H.xlsx
@@ -852,7 +852,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.002454</v>
       </c>
       <c r="J12" s="3" t="n">
         <v>0</v>
@@ -1457,7 +1457,7 @@
         <v>0.024471</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.1781</v>
+        <v>-0.180554</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>-0.139572</v>
@@ -1531,7 +1531,7 @@
         <v>0.024471</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.1781</v>
+        <v>-0.180554</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>-0.139572</v>
@@ -1720,19 +1720,19 @@
         <v>0.012126</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.11197</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.202533</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.178022</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.037062</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.004405</v>
       </c>
     </row>
     <row r="35">
@@ -1794,19 +1794,19 @@
         <v>0.051126</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.15</v>
+        <v>0.26197</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.02</v>
+        <v>0.222533</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.025</v>
+        <v>0.203022</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.011</v>
+        <v>0.048062</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.02</v>
+        <v>0.024405</v>
       </c>
     </row>
     <row r="37">
@@ -2238,19 +2238,19 @@
         <v>0.024887</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.123624</v>
+        <v>0.011654</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.240437</v>
+        <v>0.037904</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.180858</v>
+        <v>0.002836</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.039113</v>
+        <v>0.002051</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.007478</v>
+        <v>0.003073</v>
       </c>
     </row>
     <row r="49">
@@ -5692,7 +5692,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -18926,7 +18926,7 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">

--- a/output/pdf_financials_xlsx/MXL.H.xlsx
+++ b/output/pdf_financials_xlsx/MXL.H.xlsx
@@ -1473,19 +1473,19 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>0</v>
+        <v>0.001958</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0</v>
+        <v>0.129954</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0</v>
+        <v>0.188225</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0</v>
+        <v>0.259678</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0</v>
+        <v>0.009298000000000001</v>
       </c>
       <c r="G28" s="3" t="n">
         <v>0</v>
@@ -1510,19 +1510,19 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-3.206542</v>
+        <v>-3.204584</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-5.14779</v>
+        <v>-5.017836</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-11.428581</v>
+        <v>-11.240356</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-16.153944</v>
+        <v>-15.894266</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-1.070561</v>
+        <v>-1.061263</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>0.120989</v>
@@ -4225,19 +4225,19 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>0.001958</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>0.189825</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>0.274942</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>0.324457</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>0.047227</v>
       </c>
       <c r="G100" s="3" t="n">
         <v>0</v>
@@ -4672,13 +4672,13 @@
         <v>0</v>
       </c>
       <c r="C112" s="3" t="n">
-        <v>0</v>
+        <v>0.07828499999999999</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>0</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0</v>
+        <v>0.227693</v>
       </c>
       <c r="F112" s="3" t="n">
         <v>0</v>
@@ -12794,7 +12794,11 @@
           <t>Depreciation of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr"/>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E113" t="inlineStr">
         <is>
           <t>-</t>
@@ -13300,7 +13304,11 @@
           <t>Proceeds from disposal of property, plant, and equipment</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr"/>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E121" t="inlineStr">
         <is>
           <t>-</t>
@@ -15336,7 +15344,11 @@
           <t>Depreciation of property, plant and equipment (Note 9)</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr"/>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E152" t="inlineStr">
         <is>
           <t>-</t>
@@ -16840,7 +16852,11 @@
           <t>Depreciation of property, plant and equipment (Note 10)</t>
         </is>
       </c>
-      <c r="D175" t="inlineStr"/>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E175" s="5" t="n">
         <v>0.001958</v>
       </c>
@@ -19990,7 +20006,11 @@
           <t>Depreciation of property, plant and equipment (Note 9)</t>
         </is>
       </c>
-      <c r="D224" t="inlineStr"/>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E224" t="inlineStr">
         <is>
           <t>-</t>
@@ -21724,7 +21744,11 @@
           <t>Depreciation of property plant and equipment (Note 9)</t>
         </is>
       </c>
-      <c r="D251" t="inlineStr"/>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E251" t="inlineStr">
         <is>
           <t>-</t>
@@ -22772,7 +22796,11 @@
           <t>Depreciation of property, plant and equipment (Note 10)</t>
         </is>
       </c>
-      <c r="D267" t="inlineStr"/>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E267" s="5" t="n">
         <v>0.001958</v>
       </c>

--- a/output/pdf_financials_xlsx/MXL.H.xlsx
+++ b/output/pdf_financials_xlsx/MXL.H.xlsx
@@ -1175,11 +1175,15 @@
       <c r="D20" s="3" t="n">
         <v>-11.428581</v>
       </c>
-      <c r="E20" s="3" t="n">
-        <v>-16.153944</v>
-      </c>
-      <c r="F20" s="3" t="n">
-        <v>-1.070561</v>
+      <c r="E20" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F20" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G20" s="3" t="n">
         <v>0.120989</v>
@@ -1213,10 +1217,10 @@
         <v>0</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>0</v>
+        <v>-0.540465</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>0</v>
+        <v>-0.055105</v>
       </c>
       <c r="G21" s="3" t="n">
         <v>0</v>
@@ -3057,16 +3061,16 @@
         </is>
       </c>
       <c r="B70" s="3" t="n">
-        <v>0</v>
+        <v>0.288099</v>
       </c>
       <c r="C70" s="3" t="n">
-        <v>0</v>
+        <v>0.60611</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>0</v>
+        <v>0.144074</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>0</v>
+        <v>0.056246</v>
       </c>
       <c r="F70" s="3" t="n">
         <v>0</v>
@@ -3094,16 +3098,16 @@
         </is>
       </c>
       <c r="B71" s="3" t="n">
-        <v>0.055852</v>
+        <v>0.343951</v>
       </c>
       <c r="C71" s="3" t="n">
-        <v>0</v>
+        <v>0.60611</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>0</v>
+        <v>0.144074</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>0</v>
+        <v>0.056246</v>
       </c>
       <c r="F71" s="3" t="n">
         <v>0</v>
@@ -3242,16 +3246,16 @@
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>0.57185</v>
+        <v>0.283751</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>0.564007</v>
+        <v>0</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>3.332141</v>
+        <v>3.188067</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>3.69851</v>
+        <v>3.642264</v>
       </c>
       <c r="F75" s="3" t="n">
         <v>0.827897</v>
@@ -3427,17 +3431,13 @@
         </is>
       </c>
       <c r="B80" s="3" t="n">
-        <v>0.007275404516242655</v>
-      </c>
-      <c r="C80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.04480381470253845</v>
+      </c>
+      <c r="C80" s="3" t="n">
+        <v>0.04461499426256665</v>
+      </c>
+      <c r="D80" s="3" t="n">
+        <v>0.009531081431161267</v>
       </c>
       <c r="E80" s="1" t="inlineStr">
         <is>
@@ -4792,7 +4792,7 @@
         <v>0</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>0</v>
+        <v>0.05425</v>
       </c>
       <c r="G115" s="3" t="n">
         <v>0</v>
@@ -7248,7 +7248,11 @@
           <t>Current portion of lease obligations (Note 12)</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>-</t>
@@ -7442,7 +7446,11 @@
           <t>Lease obligations (Note 12)</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>-</t>
@@ -8410,7 +8418,11 @@
           <t>Current portion of lease obligations (Note 14)</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E45" t="inlineStr">
         <is>
           <t>-</t>
@@ -8544,7 +8556,11 @@
           <t>Lease obligations (Note 14)</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
           <t>-</t>
@@ -9816,7 +9832,11 @@
           <t>Current portion of lease obligations (Note 15)</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E66" s="5" t="n">
         <v>0.06586400000000001</v>
       </c>
@@ -9880,7 +9900,11 @@
           <t>Lease obligations (Note 15)</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E67" s="5" t="n">
         <v>0.288099</v>
       </c>
@@ -13174,7 +13198,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr"/>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E119" t="inlineStr">
         <is>
           <t>-</t>
@@ -13370,7 +13398,11 @@
           <t>Proceeds from disposal of marketable securities</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr"/>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E122" t="inlineStr">
         <is>
           <t>-</t>
@@ -20844,7 +20876,11 @@
           <t>Loss from discontinued operations (Note 22)</t>
         </is>
       </c>
-      <c r="D237" t="inlineStr"/>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E237" t="inlineStr">
         <is>
           <t>-</t>
